--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:46</t>
+    <t xml:space="preserve">2026-09-09 22:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:33</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:28</t>
+    <t xml:space="preserve">2026-09-27 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.74</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.02</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.48</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.18</v>
+        <v>-11.76</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-2.48</v>
+        <v>-24.75</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.73</v>
+        <v>-27.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-05 08:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
